--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84AF31CD-24C2-422E-BC99-185D42FEF01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D490D743-7DA9-4982-B2C0-2B3EC3532361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="954" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="CLASS 1ST" sheetId="19" r:id="rId4"/>
     <sheet name="CLASS 2ND" sheetId="17" r:id="rId5"/>
     <sheet name="CLASS 3RD" sheetId="2" r:id="rId6"/>
-    <sheet name="students" sheetId="7" r:id="rId7"/>
+    <sheet name="CLASS 4TH" sheetId="7" r:id="rId7"/>
     <sheet name="CLASS 5TH" sheetId="8" r:id="rId8"/>
     <sheet name="CLASS 6TH" sheetId="9" r:id="rId9"/>
     <sheet name="CLASS 7TH" sheetId="22" r:id="rId10"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACD38E2-EC2E-4E9A-948E-97ABC04AF561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5673D6-4E88-4CBB-91B5-4832B70B238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="954" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8928" tabRatio="954" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CLASS PC" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="1620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="1619">
   <si>
     <t>Other</t>
   </si>
@@ -4886,9 +4886,6 @@
   </si>
   <si>
     <t>LK54A</t>
-  </si>
-  <si>
-    <t>CLASS</t>
   </si>
   <si>
     <t>UK30A</t>
@@ -11419,8 +11416,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" customFormat="1">
-      <c r="A1" t="s">
-        <v>1618</v>
+      <c r="A1" s="27" t="s">
+        <v>343</v>
       </c>
       <c r="B1" t="s">
         <v>344</v>
@@ -12389,7 +12386,7 @@
         <v>1114</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>182</v>
@@ -12429,8 +12426,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41">
-      <c r="A1" t="s">
-        <v>1618</v>
+      <c r="A1" s="27" t="s">
+        <v>343</v>
       </c>
       <c r="B1" t="s">
         <v>344</v>
@@ -12553,7 +12550,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="2" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A2" s="5">
         <v>962</v>
       </c>
@@ -12671,7 +12668,7 @@
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
     </row>
-    <row r="4" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="4" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A4" s="5">
         <v>946</v>
       </c>
@@ -12730,7 +12727,7 @@
       <c r="AN4" s="4"/>
       <c r="AO4" s="4"/>
     </row>
-    <row r="5" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="5" spans="1:41" s="19" customFormat="1" ht="57.6">
       <c r="A5" s="5">
         <v>1105</v>
       </c>
@@ -12789,7 +12786,7 @@
       <c r="AN5" s="4"/>
       <c r="AO5" s="4"/>
     </row>
-    <row r="6" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="6" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A6" s="5">
         <v>926</v>
       </c>
@@ -12848,7 +12845,7 @@
       <c r="AN6" s="4"/>
       <c r="AO6" s="4"/>
     </row>
-    <row r="7" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="7" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A7" s="5">
         <v>827</v>
       </c>
@@ -12966,7 +12963,7 @@
       <c r="AN8" s="4"/>
       <c r="AO8" s="4"/>
     </row>
-    <row r="9" spans="1:41" s="19" customFormat="1">
+    <row r="9" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A9" s="5">
         <v>948</v>
       </c>
@@ -13025,7 +13022,7 @@
       <c r="AN9" s="4"/>
       <c r="AO9" s="4"/>
     </row>
-    <row r="10" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="10" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A10" s="5">
         <v>957</v>
       </c>
@@ -13084,7 +13081,7 @@
       <c r="AN10" s="4"/>
       <c r="AO10" s="4"/>
     </row>
-    <row r="11" spans="1:41" s="19" customFormat="1">
+    <row r="11" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A11" s="5">
         <v>1047</v>
       </c>
@@ -13143,7 +13140,7 @@
       <c r="AN11" s="4"/>
       <c r="AO11" s="4"/>
     </row>
-    <row r="12" spans="1:41" s="19" customFormat="1">
+    <row r="12" spans="1:41" s="19" customFormat="1" ht="28.8">
       <c r="A12" s="5">
         <v>1111</v>
       </c>
@@ -13202,7 +13199,7 @@
       <c r="AN12" s="4"/>
       <c r="AO12" s="4"/>
     </row>
-    <row r="13" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="13" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A13" s="5">
         <v>950</v>
       </c>
@@ -13261,7 +13258,7 @@
       <c r="AN13" s="4"/>
       <c r="AO13" s="4"/>
     </row>
-    <row r="14" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="14" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A14" s="5">
         <v>1053</v>
       </c>
@@ -13320,7 +13317,7 @@
       <c r="AN14" s="4"/>
       <c r="AO14" s="4"/>
     </row>
-    <row r="15" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="15" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A15" s="5">
         <v>1100</v>
       </c>
@@ -13379,7 +13376,7 @@
       <c r="AN15" s="4"/>
       <c r="AO15" s="4"/>
     </row>
-    <row r="16" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="16" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A16" s="5">
         <v>953</v>
       </c>
@@ -13438,7 +13435,7 @@
       <c r="AN16" s="4"/>
       <c r="AO16" s="4"/>
     </row>
-    <row r="17" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="17" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A17" s="5">
         <v>970</v>
       </c>
@@ -13497,7 +13494,7 @@
       <c r="AN17" s="4"/>
       <c r="AO17" s="4"/>
     </row>
-    <row r="18" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="18" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A18" s="5">
         <v>1038</v>
       </c>
@@ -13556,7 +13553,7 @@
       <c r="AN18" s="4"/>
       <c r="AO18" s="4"/>
     </row>
-    <row r="19" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="19" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A19" s="5">
         <v>971</v>
       </c>
@@ -13615,7 +13612,7 @@
       <c r="AN19" s="4"/>
       <c r="AO19" s="4"/>
     </row>
-    <row r="20" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="20" spans="1:41" s="19" customFormat="1" ht="57.6">
       <c r="A20" s="5">
         <v>1103</v>
       </c>
@@ -13674,7 +13671,7 @@
       <c r="AN20" s="4"/>
       <c r="AO20" s="4"/>
     </row>
-    <row r="21" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="21" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A21" s="5">
         <v>944</v>
       </c>
@@ -13733,7 +13730,7 @@
       <c r="AN21" s="4"/>
       <c r="AO21" s="4"/>
     </row>
-    <row r="22" spans="1:41" s="19" customFormat="1">
+    <row r="22" spans="1:41" s="19" customFormat="1" ht="28.8">
       <c r="A22" s="5">
         <v>1054</v>
       </c>
@@ -13792,7 +13789,7 @@
       <c r="AN22" s="4"/>
       <c r="AO22" s="4"/>
     </row>
-    <row r="23" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="23" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A23" s="5">
         <v>931</v>
       </c>
@@ -13851,7 +13848,7 @@
       <c r="AN23" s="4"/>
       <c r="AO23" s="4"/>
     </row>
-    <row r="24" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="24" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A24" s="5">
         <v>972</v>
       </c>
@@ -13910,7 +13907,7 @@
       <c r="AN24" s="4"/>
       <c r="AO24" s="4"/>
     </row>
-    <row r="25" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="25" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A25" s="5">
         <v>955</v>
       </c>
@@ -13969,7 +13966,7 @@
       <c r="AN25" s="4"/>
       <c r="AO25" s="4"/>
     </row>
-    <row r="26" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="26" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A26" s="4">
         <v>936</v>
       </c>
@@ -14028,7 +14025,7 @@
       <c r="AN26" s="4"/>
       <c r="AO26" s="4"/>
     </row>
-    <row r="27" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="27" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A27" s="5">
         <v>1107</v>
       </c>
@@ -14087,7 +14084,7 @@
       <c r="AN27" s="4"/>
       <c r="AO27" s="4"/>
     </row>
-    <row r="28" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="28" spans="1:41" s="19" customFormat="1" ht="43.2">
       <c r="A28" s="5">
         <v>976</v>
       </c>
@@ -14205,7 +14202,7 @@
       <c r="AN29" s="4"/>
       <c r="AO29" s="4"/>
     </row>
-    <row r="30" spans="1:41" s="19" customFormat="1" ht="28.8">
+    <row r="30" spans="1:41" s="19" customFormat="1" ht="57.6">
       <c r="A30" s="5">
         <v>1108</v>
       </c>
@@ -15359,7 +15356,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:41" ht="43.2">
       <c r="A2" s="10">
         <v>825</v>
       </c>
@@ -15418,7 +15415,7 @@
       <c r="AN2" s="10"/>
       <c r="AO2" s="10"/>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:41" ht="28.8">
       <c r="A3" s="10">
         <v>1001</v>
       </c>
@@ -15477,7 +15474,7 @@
       <c r="AN3" s="10"/>
       <c r="AO3" s="10"/>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:41" ht="28.8">
       <c r="A4" s="10">
         <v>789</v>
       </c>
@@ -15534,7 +15531,7 @@
       <c r="AN4" s="10"/>
       <c r="AO4" s="10"/>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:41" ht="28.8">
       <c r="A5" s="10">
         <v>1115</v>
       </c>
@@ -15593,7 +15590,7 @@
       <c r="AN5" s="10"/>
       <c r="AO5" s="10"/>
     </row>
-    <row r="6" spans="1:41" ht="28.8">
+    <row r="6" spans="1:41" ht="43.2">
       <c r="A6" s="10">
         <v>816</v>
       </c>
@@ -15652,7 +15649,7 @@
       <c r="AN6" s="10"/>
       <c r="AO6" s="10"/>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:41" ht="43.2">
       <c r="A7" s="10">
         <v>1119</v>
       </c>
@@ -15711,7 +15708,7 @@
       <c r="AN7" s="10"/>
       <c r="AO7" s="10"/>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:41" ht="57.6">
       <c r="A8" s="10">
         <v>804</v>
       </c>
@@ -15770,7 +15767,7 @@
       <c r="AN8" s="10"/>
       <c r="AO8" s="10"/>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:41" ht="28.8">
       <c r="A9" s="10">
         <v>674</v>
       </c>
@@ -15829,7 +15826,7 @@
       <c r="AN9" s="10"/>
       <c r="AO9" s="10"/>
     </row>
-    <row r="10" spans="1:41" ht="28.8">
+    <row r="10" spans="1:41" ht="43.2">
       <c r="A10" s="10">
         <v>854</v>
       </c>
@@ -15888,7 +15885,7 @@
       <c r="AN10" s="10"/>
       <c r="AO10" s="10"/>
     </row>
-    <row r="11" spans="1:41" ht="28.8">
+    <row r="11" spans="1:41" ht="43.2">
       <c r="A11" s="10">
         <v>847</v>
       </c>
@@ -15947,7 +15944,7 @@
       <c r="AN11" s="10"/>
       <c r="AO11" s="10"/>
     </row>
-    <row r="12" spans="1:41" ht="28.8">
+    <row r="12" spans="1:41" ht="43.2">
       <c r="A12" s="10">
         <v>791</v>
       </c>
@@ -16006,7 +16003,7 @@
       <c r="AN12" s="10"/>
       <c r="AO12" s="10"/>
     </row>
-    <row r="13" spans="1:41" ht="28.8">
+    <row r="13" spans="1:41" ht="43.2">
       <c r="A13" s="10">
         <v>924</v>
       </c>
@@ -16065,7 +16062,7 @@
       <c r="AN13" s="10"/>
       <c r="AO13" s="10"/>
     </row>
-    <row r="14" spans="1:41" ht="28.8">
+    <row r="14" spans="1:41" ht="43.2">
       <c r="A14" s="10">
         <v>991</v>
       </c>
@@ -16124,7 +16121,7 @@
       <c r="AN14" s="10"/>
       <c r="AO14" s="10"/>
     </row>
-    <row r="15" spans="1:41" ht="28.8">
+    <row r="15" spans="1:41" ht="43.2">
       <c r="A15" s="10">
         <v>787</v>
       </c>
@@ -16183,7 +16180,7 @@
       <c r="AN15" s="10"/>
       <c r="AO15" s="10"/>
     </row>
-    <row r="16" spans="1:41" ht="28.8">
+    <row r="16" spans="1:41" ht="43.2">
       <c r="A16" s="10">
         <v>997</v>
       </c>
@@ -16242,7 +16239,7 @@
       <c r="AN16" s="10"/>
       <c r="AO16" s="10"/>
     </row>
-    <row r="17" spans="1:41" ht="28.8">
+    <row r="17" spans="1:41" ht="43.2">
       <c r="A17" s="10">
         <v>923</v>
       </c>
@@ -16301,7 +16298,7 @@
       <c r="AN17" s="10"/>
       <c r="AO17" s="10"/>
     </row>
-    <row r="18" spans="1:41" ht="43.2">
+    <row r="18" spans="1:41" ht="72">
       <c r="A18" s="10">
         <v>1000</v>
       </c>
@@ -16360,7 +16357,7 @@
       <c r="AN18" s="10"/>
       <c r="AO18" s="10"/>
     </row>
-    <row r="19" spans="1:41" ht="28.8">
+    <row r="19" spans="1:41" ht="43.2">
       <c r="A19" s="10">
         <v>814</v>
       </c>
@@ -16419,7 +16416,7 @@
       <c r="AN19" s="10"/>
       <c r="AO19" s="10"/>
     </row>
-    <row r="20" spans="1:41" ht="28.8">
+    <row r="20" spans="1:41" ht="43.2">
       <c r="A20" s="10">
         <v>851</v>
       </c>
@@ -16537,7 +16534,7 @@
       <c r="AN21" s="10"/>
       <c r="AO21" s="10"/>
     </row>
-    <row r="22" spans="1:41" ht="28.8">
+    <row r="22" spans="1:41" ht="43.2">
       <c r="A22" s="10">
         <v>834</v>
       </c>
@@ -16596,7 +16593,7 @@
       <c r="AN22" s="10"/>
       <c r="AO22" s="10"/>
     </row>
-    <row r="23" spans="1:41">
+    <row r="23" spans="1:41" ht="43.2">
       <c r="A23" s="10">
         <v>812</v>
       </c>
@@ -16655,7 +16652,7 @@
       <c r="AN23" s="10"/>
       <c r="AO23" s="10"/>
     </row>
-    <row r="24" spans="1:41" ht="28.8">
+    <row r="24" spans="1:41" ht="43.2">
       <c r="A24" s="10">
         <v>853</v>
       </c>
@@ -16714,7 +16711,7 @@
       <c r="AN24" s="10"/>
       <c r="AO24" s="10"/>
     </row>
-    <row r="25" spans="1:41" ht="28.8">
+    <row r="25" spans="1:41" ht="43.2">
       <c r="A25" s="10">
         <v>990</v>
       </c>
@@ -16773,7 +16770,7 @@
       <c r="AN25" s="10"/>
       <c r="AO25" s="10"/>
     </row>
-    <row r="26" spans="1:41">
+    <row r="26" spans="1:41" ht="57.6">
       <c r="A26" s="10">
         <v>803</v>
       </c>
@@ -16832,7 +16829,7 @@
       <c r="AN26" s="10"/>
       <c r="AO26" s="10"/>
     </row>
-    <row r="27" spans="1:41">
+    <row r="27" spans="1:41" ht="43.2">
       <c r="A27" s="10">
         <v>790</v>
       </c>
@@ -16891,7 +16888,7 @@
       <c r="AN27" s="10"/>
       <c r="AO27" s="10"/>
     </row>
-    <row r="28" spans="1:41">
+    <row r="28" spans="1:41" ht="43.2">
       <c r="A28" s="10">
         <v>1003</v>
       </c>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5673D6-4E88-4CBB-91B5-4832B70B238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DB235A-474C-4A7F-AC8B-F5CEF9C91771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8928" tabRatio="954" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="954" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CLASS PC" sheetId="1" r:id="rId1"/>
@@ -11406,7 +11406,7 @@
   <dimension ref="A1:AO31"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" style="19" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="18"/>
     <col min="3" max="3" width="9.88671875" style="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="18"/>
@@ -12421,6 +12421,7 @@
   <dimension ref="A1:AO30"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -14271,7 +14272,7 @@
   <dimension ref="A1:AO32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="10"/>
+    <col min="1" max="1" width="13.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="16" customWidth="1"/>
     <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.5546875" bestFit="1" customWidth="1"/>
